--- a/all_sim/gemini_domain.xlsx
+++ b/all_sim/gemini_domain.xlsx
@@ -331,7 +331,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="34.1" min="1" max="1" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="2" max="2" bestFit="1" customWidth="1"/>
+    <col width="23.1" min="2" max="2" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="3" max="3" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="4" max="4" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="5" max="5" bestFit="1" customWidth="1"/>
@@ -339,7 +339,7 @@
     <col width="24.200000000000003" min="7" max="7" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="8" max="8" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="9" max="9" bestFit="1" customWidth="1"/>
-    <col width="25.3" min="10" max="10" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="10" max="10" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="11" max="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -350,34 +350,34 @@
         </is>
       </c>
       <c r="B1" s="0" t="n">
-        <v>0.975</v>
+        <v>0.9875</v>
       </c>
       <c r="C1" s="0" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.8571428571428572</v>
       </c>
       <c r="D1" s="0" t="n">
-        <v>0.31479591836734705</v>
+        <v>0.6573979591836735</v>
       </c>
       <c r="E1" s="0" t="n">
-        <v>0.33571428571428574</v>
+        <v>0.6428571428571428</v>
       </c>
       <c r="F1" s="0" t="n">
-        <v>0.3407142857142857</v>
+        <v>0.6453571428571429</v>
       </c>
       <c r="G1" s="0" t="n">
-        <v>0.3407142857142857</v>
+        <v>0.6453571428571429</v>
       </c>
       <c r="H1" s="0" t="n">
-        <v>0.34071428571428575</v>
+        <v>0.6447161172161172</v>
       </c>
       <c r="I1" s="0" t="n">
-        <v>0.37142857142857144</v>
+        <v>0.6600732600732601</v>
       </c>
       <c r="J1" s="0" t="n">
-        <v>0.3821428571428571</v>
+        <v>0.6654304029304029</v>
       </c>
       <c r="K1" s="0" t="n">
-        <v>0.3538095238095238</v>
+        <v>0.6505889724310777</v>
       </c>
     </row>
     <row r="2">
@@ -387,34 +387,34 @@
         </is>
       </c>
       <c r="B2" s="0" t="n">
-        <v>0.373015873015873</v>
+        <v>0.6865079365079365</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>0.373015873015873</v>
+        <v>0.6865079365079365</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>0.45634920634920634</v>
+        <v>0.7281746031746031</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>0.4785714285714285</v>
+        <v>0.7392857142857142</v>
       </c>
       <c r="F2" s="0" t="n">
-        <v>0.4785714285714285</v>
+        <v>0.7392857142857142</v>
       </c>
       <c r="G2" s="0" t="n">
-        <v>0.4785714285714285</v>
+        <v>0.7392857142857142</v>
       </c>
       <c r="H2" s="0" t="n">
-        <v>0.4785714285714285</v>
+        <v>0.7392857142857142</v>
       </c>
       <c r="I2" s="0" t="n">
-        <v>0.4785714285714285</v>
+        <v>0.7392857142857142</v>
       </c>
       <c r="J2" s="0" t="n">
-        <v>0.4785714285714285</v>
+        <v>0.7392857142857142</v>
       </c>
       <c r="K2" s="0" t="n">
-        <v>0.4785714285714285</v>
+        <v>0.7392857142857142</v>
       </c>
     </row>
     <row r="3">
@@ -424,34 +424,34 @@
         </is>
       </c>
       <c r="B3" s="0" t="n">
-        <v>0.45</v>
+        <v>0.725</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>0.45</v>
+        <v>0.725</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>0.45</v>
+        <v>0.725</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>0.45</v>
+        <v>0.725</v>
       </c>
       <c r="F3" s="0" t="n">
-        <v>0.45</v>
+        <v>0.725</v>
       </c>
       <c r="G3" s="0" t="n">
-        <v>0.45</v>
+        <v>0.725</v>
       </c>
       <c r="H3" s="0" t="n">
-        <v>0.45</v>
+        <v>0.725</v>
       </c>
       <c r="I3" s="0" t="n">
-        <v>0.45</v>
+        <v>0.725</v>
       </c>
       <c r="J3" s="0" t="n">
-        <v>0.45</v>
+        <v>0.725</v>
       </c>
       <c r="K3" s="0" t="n">
-        <v>0.45</v>
+        <v>0.725</v>
       </c>
     </row>
     <row r="4">
@@ -461,34 +461,34 @@
         </is>
       </c>
       <c r="B4" s="0" t="n">
-        <v>0.05531669976114421</v>
+        <v>0.4541289381158662</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>0.06020522687189353</v>
+        <v>0.455475747764305</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>0.07434931323820214</v>
+        <v>0.46141708086152533</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>0.0748637165303832</v>
+        <v>0.4616742825076159</v>
       </c>
       <c r="F4" s="0" t="n">
-        <v>0.07434931323820214</v>
+        <v>0.46141708086152533</v>
       </c>
       <c r="G4" s="0" t="n">
-        <v>0.04265538987761211</v>
+        <v>0.44320269493880604</v>
       </c>
       <c r="H4" s="0" t="n">
-        <v>0.07580834803057025</v>
+        <v>0.45853909465020576</v>
       </c>
       <c r="I4" s="0" t="n">
-        <v>0.02962962962962963</v>
+        <v>0.4354497354497355</v>
       </c>
       <c r="J4" s="0" t="n">
-        <v>0.031525573192239864</v>
+        <v>0.43763778659611996</v>
       </c>
       <c r="K4" s="0" t="n">
-        <v>0.01936026936026936</v>
+        <v>0.43275705775705775</v>
       </c>
     </row>
     <row r="5">
@@ -498,34 +498,34 @@
         </is>
       </c>
       <c r="B5" s="0" t="n">
-        <v>0.140625</v>
+        <v>0.5551609848484849</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.47409909909909914</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>0.025</v>
+        <v>0.41493902439024394</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>0.125</v>
+        <v>0.38808139534883723</v>
       </c>
       <c r="F5" s="0" t="n">
-        <v>0.125</v>
+        <v>0.4910714285714286</v>
       </c>
       <c r="G5" s="0" t="n">
-        <v>0.125</v>
+        <v>0.4910714285714286</v>
       </c>
       <c r="H5" s="0" t="n">
-        <v>0.125</v>
+        <v>0.4910714285714286</v>
       </c>
       <c r="I5" s="0" t="n">
-        <v>0.125</v>
+        <v>0.4910714285714286</v>
       </c>
       <c r="J5" s="0" t="n">
-        <v>0.125</v>
+        <v>0.4910714285714286</v>
       </c>
       <c r="K5" s="0" t="n">
-        <v>0.125</v>
+        <v>0.4910714285714286</v>
       </c>
     </row>
     <row r="6">
@@ -541,28 +541,28 @@
         <v>1.0</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.6428571428571428</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.6428571428571428</v>
       </c>
       <c r="F6" s="0" t="n">
-        <v>0.09999999999999998</v>
+        <v>0.55</v>
       </c>
       <c r="G6" s="0" t="n">
-        <v>0.09999999999999998</v>
+        <v>0.55</v>
       </c>
       <c r="H6" s="0" t="n">
-        <v>0.09999999999999998</v>
+        <v>0.55</v>
       </c>
       <c r="I6" s="0" t="n">
-        <v>0.09999999999999998</v>
+        <v>0.55</v>
       </c>
       <c r="J6" s="0" t="n">
-        <v>0.09999999999999998</v>
+        <v>0.55</v>
       </c>
       <c r="K6" s="0" t="n">
-        <v>0.09999999999999998</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="7">
@@ -572,34 +572,34 @@
         </is>
       </c>
       <c r="B7" s="0" t="n">
-        <v>0.26666666666666666</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>0.1833333333333333</v>
+        <v>0.5916666666666667</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>0.26666666666666666</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>0.26666666666666666</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="F7" s="0" t="n">
-        <v>0.26666666666666666</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="G7" s="0" t="n">
-        <v>0.26666666666666666</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="H7" s="0" t="n">
-        <v>0.26666666666666666</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="I7" s="0" t="n">
-        <v>0.26666666666666666</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="J7" s="0" t="n">
-        <v>0.26666666666666666</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="K7" s="0" t="n">
-        <v>0.26666666666666666</v>
+        <v>0.6333333333333333</v>
       </c>
     </row>
     <row r="8">
@@ -609,34 +609,34 @@
         </is>
       </c>
       <c r="B8" s="0" t="n">
-        <v>0.763888888888889</v>
+        <v>0.8819444444444444</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.9166666666666667</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.8541666666666667</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.8541666666666667</v>
       </c>
       <c r="F8" s="0" t="n">
-        <v>0.7416666666666667</v>
+        <v>0.8708333333333333</v>
       </c>
       <c r="G8" s="0" t="n">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="H8" s="0" t="n">
-        <v>0.8250000000000001</v>
+        <v>0.9125000000000001</v>
       </c>
       <c r="I8" s="0" t="n">
-        <v>0.6722222222222222</v>
+        <v>0.836111111111111</v>
       </c>
       <c r="J8" s="0" t="n">
-        <v>0.6722222222222222</v>
+        <v>0.836111111111111</v>
       </c>
       <c r="K8" s="0" t="n">
-        <v>0.6722222222222222</v>
+        <v>0.836111111111111</v>
       </c>
     </row>
     <row r="9">
@@ -646,34 +646,34 @@
         </is>
       </c>
       <c r="B9" s="0" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8333333333333333</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8333333333333333</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8333333333333333</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>0.6190476190476191</v>
+        <v>0.780952380952381</v>
       </c>
       <c r="F9" s="0" t="n">
-        <v>0.5</v>
+        <v>0.7196969696969697</v>
       </c>
       <c r="G9" s="0" t="n">
-        <v>0.5507936507936508</v>
+        <v>0.7450937950937951</v>
       </c>
       <c r="H9" s="0" t="n">
-        <v>0.4992063492063492</v>
+        <v>0.7183531746031746</v>
       </c>
       <c r="I9" s="0" t="n">
-        <v>0.4992063492063492</v>
+        <v>0.7183531746031746</v>
       </c>
       <c r="J9" s="0" t="n">
-        <v>0.4992063492063492</v>
+        <v>0.7183531746031746</v>
       </c>
       <c r="K9" s="0" t="n">
-        <v>0.46428571428571425</v>
+        <v>0.7008928571428571</v>
       </c>
     </row>
     <row r="10">
@@ -683,34 +683,34 @@
         </is>
       </c>
       <c r="B10" s="0" t="n">
-        <v>0.25</v>
+        <v>0.625</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>0.25</v>
+        <v>0.625</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>0.25</v>
+        <v>0.625</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>0.25</v>
+        <v>0.625</v>
       </c>
       <c r="F10" s="0" t="n">
-        <v>0.25</v>
+        <v>0.625</v>
       </c>
       <c r="G10" s="0" t="n">
-        <v>0.25</v>
+        <v>0.625</v>
       </c>
       <c r="H10" s="0" t="n">
-        <v>0.25</v>
+        <v>0.625</v>
       </c>
       <c r="I10" s="0" t="n">
-        <v>0.25</v>
+        <v>0.625</v>
       </c>
       <c r="J10" s="0" t="n">
-        <v>0.25</v>
+        <v>0.625</v>
       </c>
       <c r="K10" s="0" t="n">
-        <v>0.25</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="11">
@@ -720,34 +720,34 @@
         </is>
       </c>
       <c r="B11" s="0" t="n">
-        <v>1.0</v>
+        <v>0.9838709677419355</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>1.0</v>
+        <v>0.9838709677419355</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.6197916666666666</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>0.25</v>
+        <v>0.5514705882352942</v>
       </c>
       <c r="F11" s="0" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="G11" s="0" t="n">
-        <v>0.14285714285714285</v>
+        <v>0.5089285714285714</v>
       </c>
       <c r="H11" s="0" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="I11" s="0" t="n">
-        <v>0.125</v>
+        <v>0.48355263157894735</v>
       </c>
       <c r="J11" s="0" t="n">
-        <v>0.05</v>
+        <v>0.3617346938775511</v>
       </c>
       <c r="K11" s="0" t="n">
-        <v>0.2962962962962963</v>
+        <v>0.4814814814814815</v>
       </c>
     </row>
     <row r="12">
@@ -757,34 +757,34 @@
         </is>
       </c>
       <c r="B12" s="0" t="n">
-        <v>0.33333333333333337</v>
+        <v>0.6266666666666667</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>0.33333333333333337</v>
+        <v>0.6266666666666667</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>0.33333333333333337</v>
+        <v>0.6266666666666667</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>0.2777777777777778</v>
+        <v>0.5988888888888889</v>
       </c>
       <c r="F12" s="0" t="n">
-        <v>0.2777777777777778</v>
+        <v>0.5988888888888889</v>
       </c>
       <c r="G12" s="0" t="n">
-        <v>0.2777777777777778</v>
+        <v>0.5988888888888889</v>
       </c>
       <c r="H12" s="0" t="n">
-        <v>0.3888888888888889</v>
+        <v>0.6527777777777778</v>
       </c>
       <c r="I12" s="0" t="n">
-        <v>0.3888888888888889</v>
+        <v>0.6527777777777778</v>
       </c>
       <c r="J12" s="0" t="n">
-        <v>0.3888888888888889</v>
+        <v>0.6527777777777778</v>
       </c>
       <c r="K12" s="0" t="n">
-        <v>0.3888888888888889</v>
+        <v>0.6527777777777778</v>
       </c>
     </row>
     <row r="13">
@@ -794,34 +794,34 @@
         </is>
       </c>
       <c r="B13" s="0" t="n">
-        <v>0.29924242424242425</v>
+        <v>0.6496212121212122</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>0.29924242424242425</v>
+        <v>0.6496212121212122</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>0.2784382284382284</v>
+        <v>0.6392191142191141</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>0.2784382284382284</v>
+        <v>0.6392191142191141</v>
       </c>
       <c r="F13" s="0" t="n">
-        <v>0.2784382284382284</v>
+        <v>0.6392191142191141</v>
       </c>
       <c r="G13" s="0" t="n">
-        <v>0.2784382284382284</v>
+        <v>0.6392191142191141</v>
       </c>
       <c r="H13" s="0" t="n">
-        <v>0.2784382284382284</v>
+        <v>0.6392191142191141</v>
       </c>
       <c r="I13" s="0" t="n">
-        <v>0.2784382284382284</v>
+        <v>0.6392191142191141</v>
       </c>
       <c r="J13" s="0" t="n">
-        <v>0.2784382284382284</v>
+        <v>0.6392191142191141</v>
       </c>
       <c r="K13" s="0" t="n">
-        <v>0.2784382284382284</v>
+        <v>0.6392191142191141</v>
       </c>
     </row>
     <row r="14">
@@ -831,34 +831,34 @@
         </is>
       </c>
       <c r="B14" s="0" t="n">
-        <v>0.3666666666666667</v>
+        <v>0.6694444444444445</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>0.3666666666666667</v>
+        <v>0.6694444444444445</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>0.3666666666666667</v>
+        <v>0.6694444444444445</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>0.3666666666666667</v>
+        <v>0.6694444444444445</v>
       </c>
       <c r="F14" s="0" t="n">
-        <v>0.3666666666666667</v>
+        <v>0.6694444444444445</v>
       </c>
       <c r="G14" s="0" t="n">
-        <v>0.3666666666666667</v>
+        <v>0.6694444444444445</v>
       </c>
       <c r="H14" s="0" t="n">
-        <v>0.3666666666666667</v>
+        <v>0.6694444444444445</v>
       </c>
       <c r="I14" s="0" t="n">
-        <v>0.3666666666666667</v>
+        <v>0.6694444444444445</v>
       </c>
       <c r="J14" s="0" t="n">
-        <v>0.3666666666666667</v>
+        <v>0.6694444444444445</v>
       </c>
       <c r="K14" s="0" t="n">
-        <v>0.3666666666666667</v>
+        <v>0.6694444444444445</v>
       </c>
     </row>
     <row r="15">
@@ -868,34 +868,34 @@
         </is>
       </c>
       <c r="B15" s="0" t="n">
-        <v>0.5</v>
+        <v>0.6833333333333333</v>
       </c>
       <c r="C15" s="0" t="n">
-        <v>0.4</v>
+        <v>0.6615384615384616</v>
       </c>
       <c r="D15" s="0" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5745614035087719</v>
       </c>
       <c r="E15" s="0" t="n">
-        <v>0.4</v>
+        <v>0.578048780487805</v>
       </c>
       <c r="F15" s="0" t="n">
-        <v>0.4</v>
+        <v>0.5604651162790697</v>
       </c>
       <c r="G15" s="0" t="n">
-        <v>0.4</v>
+        <v>0.48703703703703705</v>
       </c>
       <c r="H15" s="0" t="n">
-        <v>0.4</v>
+        <v>0.51</v>
       </c>
       <c r="I15" s="0" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4766666666666667</v>
       </c>
       <c r="J15" s="0" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4385964912280702</v>
       </c>
       <c r="K15" s="0" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.40690208667736755</v>
       </c>
     </row>
     <row r="16">
@@ -905,34 +905,34 @@
         </is>
       </c>
       <c r="B16" s="0" t="n">
-        <v>0.7624338624338625</v>
+        <v>0.8230773963332103</v>
       </c>
       <c r="C16" s="0" t="n">
-        <v>0.7624338624338625</v>
+        <v>0.8230773963332103</v>
       </c>
       <c r="D16" s="0" t="n">
-        <v>0.49955908289241624</v>
+        <v>0.6942239858906525</v>
       </c>
       <c r="E16" s="0" t="n">
-        <v>0.58505291005291</v>
+        <v>0.7357082732082731</v>
       </c>
       <c r="F16" s="0" t="n">
-        <v>0.26406325156325156</v>
+        <v>0.5799482924482925</v>
       </c>
       <c r="G16" s="0" t="n">
-        <v>0.3568121693121693</v>
+        <v>0.6240582585691281</v>
       </c>
       <c r="H16" s="0" t="n">
-        <v>0.36468253968253966</v>
+        <v>0.6291497804795677</v>
       </c>
       <c r="I16" s="0" t="n">
-        <v>0.3094155844155844</v>
+        <v>0.6026244588744589</v>
       </c>
       <c r="J16" s="0" t="n">
-        <v>0.3094155844155844</v>
+        <v>0.6026244588744589</v>
       </c>
       <c r="K16" s="0" t="n">
-        <v>0.36005291005291</v>
+        <v>0.6256786289394984</v>
       </c>
     </row>
     <row r="17">
@@ -942,34 +942,34 @@
         </is>
       </c>
       <c r="B17" s="0" t="n">
-        <v>0.4</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="C17" s="0" t="n">
-        <v>0.4</v>
+        <v>0.5928571428571429</v>
       </c>
       <c r="D17" s="0" t="n">
-        <v>0.4</v>
+        <v>0.5928571428571429</v>
       </c>
       <c r="E17" s="0" t="n">
-        <v>0.4</v>
+        <v>0.5928571428571429</v>
       </c>
       <c r="F17" s="0" t="n">
-        <v>0.4</v>
+        <v>0.5928571428571429</v>
       </c>
       <c r="G17" s="0" t="n">
-        <v>0.4</v>
+        <v>0.5928571428571429</v>
       </c>
       <c r="H17" s="0" t="n">
-        <v>0.4</v>
+        <v>0.5928571428571429</v>
       </c>
       <c r="I17" s="0" t="n">
-        <v>0.4</v>
+        <v>0.5928571428571429</v>
       </c>
       <c r="J17" s="0" t="n">
-        <v>0.4</v>
+        <v>0.5928571428571429</v>
       </c>
       <c r="K17" s="0" t="n">
-        <v>0.4</v>
+        <v>0.5928571428571429</v>
       </c>
     </row>
     <row r="18">
@@ -979,34 +979,34 @@
         </is>
       </c>
       <c r="B18" s="0" t="n">
-        <v>0.3946428571428572</v>
+        <v>0.6973214285714286</v>
       </c>
       <c r="C18" s="0" t="n">
-        <v>0.96875</v>
+        <v>0.9692234848484849</v>
       </c>
       <c r="D18" s="0" t="n">
-        <v>0.96875</v>
+        <v>0.9692234848484849</v>
       </c>
       <c r="E18" s="0" t="n">
-        <v>0.96875</v>
+        <v>0.9692234848484849</v>
       </c>
       <c r="F18" s="0" t="n">
-        <v>0.3946428571428572</v>
+        <v>0.6973214285714286</v>
       </c>
       <c r="G18" s="0" t="n">
-        <v>0.96875</v>
+        <v>0.984375</v>
       </c>
       <c r="H18" s="0" t="n">
-        <v>0.96875</v>
+        <v>0.984375</v>
       </c>
       <c r="I18" s="0" t="n">
-        <v>0.96875</v>
+        <v>0.9692234848484849</v>
       </c>
       <c r="J18" s="0" t="n">
-        <v>0.7416666666666667</v>
+        <v>0.8422619047619048</v>
       </c>
       <c r="K18" s="0" t="n">
-        <v>0.3522727272727273</v>
+        <v>0.5584893048128342</v>
       </c>
     </row>
     <row r="19">
@@ -1016,34 +1016,34 @@
         </is>
       </c>
       <c r="B19" s="0" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="C19" s="0" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="D19" s="0" t="n">
-        <v>0.25</v>
+        <v>0.625</v>
       </c>
       <c r="E19" s="0" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="F19" s="0" t="n">
-        <v>0.25</v>
+        <v>0.625</v>
       </c>
       <c r="G19" s="0" t="n">
-        <v>0.25</v>
+        <v>0.625</v>
       </c>
       <c r="H19" s="0" t="n">
-        <v>0.25</v>
+        <v>0.625</v>
       </c>
       <c r="I19" s="0" t="n">
-        <v>0.25</v>
+        <v>0.625</v>
       </c>
       <c r="J19" s="0" t="n">
-        <v>0.25</v>
+        <v>0.625</v>
       </c>
       <c r="K19" s="0" t="n">
-        <v>0.25</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="20">
@@ -1053,34 +1053,34 @@
         </is>
       </c>
       <c r="B20" s="0" t="n">
-        <v>0.31726190476190474</v>
+        <v>0.6586309523809524</v>
       </c>
       <c r="C20" s="0" t="n">
-        <v>0.25476190476190474</v>
+        <v>0.6273809523809524</v>
       </c>
       <c r="D20" s="0" t="n">
-        <v>0.25476190476190474</v>
+        <v>0.6273809523809524</v>
       </c>
       <c r="E20" s="0" t="n">
-        <v>0.25476190476190474</v>
+        <v>0.6273809523809524</v>
       </c>
       <c r="F20" s="0" t="n">
-        <v>0.25476190476190474</v>
+        <v>0.6273809523809524</v>
       </c>
       <c r="G20" s="0" t="n">
-        <v>0.25476190476190474</v>
+        <v>0.6273809523809524</v>
       </c>
       <c r="H20" s="0" t="n">
-        <v>0.25476190476190474</v>
+        <v>0.6273809523809524</v>
       </c>
       <c r="I20" s="0" t="n">
-        <v>0.25476190476190474</v>
+        <v>0.6273809523809524</v>
       </c>
       <c r="J20" s="0" t="n">
-        <v>0.25476190476190474</v>
+        <v>0.6273809523809524</v>
       </c>
       <c r="K20" s="0" t="n">
-        <v>0.25476190476190474</v>
+        <v>0.6273809523809524</v>
       </c>
     </row>
     <row r="21">

--- a/all_sim/gemini_domain.xlsx
+++ b/all_sim/gemini_domain.xlsx
@@ -331,15 +331,15 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="34.1" min="1" max="1" bestFit="1" customWidth="1"/>
-    <col width="23.1" min="2" max="2" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="3" max="3" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="2" max="2" bestFit="1" customWidth="1"/>
+    <col width="25.3" min="3" max="3" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="4" max="4" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="5" max="5" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="6" max="6" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="7" max="7" bestFit="1" customWidth="1"/>
+    <col width="25.3" min="7" max="7" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="8" max="8" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="9" max="9" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="10" max="10" bestFit="1" customWidth="1"/>
+    <col width="25.3" min="9" max="9" bestFit="1" customWidth="1"/>
+    <col width="25.3" min="10" max="10" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="11" max="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -350,34 +350,34 @@
         </is>
       </c>
       <c r="B1" s="0" t="n">
-        <v>0.9875</v>
+        <v>0.975</v>
       </c>
       <c r="C1" s="0" t="n">
-        <v>0.8571428571428572</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="D1" s="0" t="n">
-        <v>0.6573979591836735</v>
+        <v>0.31479591836734705</v>
       </c>
       <c r="E1" s="0" t="n">
-        <v>0.6428571428571428</v>
+        <v>0.31892857142857145</v>
       </c>
       <c r="F1" s="0" t="n">
-        <v>0.6453571428571429</v>
+        <v>0.32367857142857137</v>
       </c>
       <c r="G1" s="0" t="n">
-        <v>0.6453571428571429</v>
+        <v>0.32367857142857137</v>
       </c>
       <c r="H1" s="0" t="n">
-        <v>0.6447161172161172</v>
+        <v>0.32324175824175827</v>
       </c>
       <c r="I1" s="0" t="n">
-        <v>0.6600732600732601</v>
+        <v>0.3523809523809524</v>
       </c>
       <c r="J1" s="0" t="n">
-        <v>0.6654304029304029</v>
+        <v>0.3625457875457875</v>
       </c>
       <c r="K1" s="0" t="n">
-        <v>0.6505889724310777</v>
+        <v>0.33518796992481203</v>
       </c>
     </row>
     <row r="2">
@@ -387,34 +387,34 @@
         </is>
       </c>
       <c r="B2" s="0" t="n">
-        <v>0.6865079365079365</v>
+        <v>0.373015873015873</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>0.6865079365079365</v>
+        <v>0.373015873015873</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>0.7281746031746031</v>
+        <v>0.45634920634920634</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>0.7392857142857142</v>
+        <v>0.4785714285714285</v>
       </c>
       <c r="F2" s="0" t="n">
-        <v>0.7392857142857142</v>
+        <v>0.4785714285714285</v>
       </c>
       <c r="G2" s="0" t="n">
-        <v>0.7392857142857142</v>
+        <v>0.4785714285714285</v>
       </c>
       <c r="H2" s="0" t="n">
-        <v>0.7392857142857142</v>
+        <v>0.4785714285714285</v>
       </c>
       <c r="I2" s="0" t="n">
-        <v>0.7392857142857142</v>
+        <v>0.4785714285714285</v>
       </c>
       <c r="J2" s="0" t="n">
-        <v>0.7392857142857142</v>
+        <v>0.4785714285714285</v>
       </c>
       <c r="K2" s="0" t="n">
-        <v>0.7392857142857142</v>
+        <v>0.4785714285714285</v>
       </c>
     </row>
     <row r="3">
@@ -424,34 +424,34 @@
         </is>
       </c>
       <c r="B3" s="0" t="n">
-        <v>0.725</v>
+        <v>0.45</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>0.725</v>
+        <v>0.45</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>0.725</v>
+        <v>0.45</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>0.725</v>
+        <v>0.45</v>
       </c>
       <c r="F3" s="0" t="n">
-        <v>0.725</v>
+        <v>0.45</v>
       </c>
       <c r="G3" s="0" t="n">
-        <v>0.725</v>
+        <v>0.45</v>
       </c>
       <c r="H3" s="0" t="n">
-        <v>0.725</v>
+        <v>0.45</v>
       </c>
       <c r="I3" s="0" t="n">
-        <v>0.725</v>
+        <v>0.45</v>
       </c>
       <c r="J3" s="0" t="n">
-        <v>0.725</v>
+        <v>0.45</v>
       </c>
       <c r="K3" s="0" t="n">
-        <v>0.725</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="4">
@@ -461,34 +461,34 @@
         </is>
       </c>
       <c r="B4" s="0" t="n">
-        <v>0.4541289381158662</v>
+        <v>0.04718189097274064</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>0.455475747764305</v>
+        <v>0.051219372114894496</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>0.46141708086152533</v>
+        <v>0.06308426577786848</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>0.4616742825076159</v>
+        <v>0.06352072917729484</v>
       </c>
       <c r="F4" s="0" t="n">
-        <v>0.46141708086152533</v>
+        <v>0.06308426577786848</v>
       </c>
       <c r="G4" s="0" t="n">
-        <v>0.44320269493880604</v>
+        <v>0.035990485209235215</v>
       </c>
       <c r="H4" s="0" t="n">
-        <v>0.45853909465020576</v>
+        <v>0.06377527691460672</v>
       </c>
       <c r="I4" s="0" t="n">
-        <v>0.4354497354497355</v>
+        <v>0.024926513815402705</v>
       </c>
       <c r="J4" s="0" t="n">
-        <v>0.43763778659611996</v>
+        <v>0.026599702380952384</v>
       </c>
       <c r="K4" s="0" t="n">
-        <v>0.43275705775705775</v>
+        <v>0.01638176638176638</v>
       </c>
     </row>
     <row r="5">
@@ -498,34 +498,34 @@
         </is>
       </c>
       <c r="B5" s="0" t="n">
-        <v>0.5551609848484849</v>
+        <v>0.13636363636363635</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>0.47409909909909914</v>
+        <v>0.07207207207207207</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>0.41493902439024394</v>
+        <v>0.0201219512195122</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>0.38808139534883723</v>
+        <v>0.08139534883720931</v>
       </c>
       <c r="F5" s="0" t="n">
-        <v>0.4910714285714286</v>
+        <v>0.10714285714285715</v>
       </c>
       <c r="G5" s="0" t="n">
-        <v>0.4910714285714286</v>
+        <v>0.10714285714285715</v>
       </c>
       <c r="H5" s="0" t="n">
-        <v>0.4910714285714286</v>
+        <v>0.10714285714285715</v>
       </c>
       <c r="I5" s="0" t="n">
-        <v>0.4910714285714286</v>
+        <v>0.10714285714285715</v>
       </c>
       <c r="J5" s="0" t="n">
-        <v>0.4910714285714286</v>
+        <v>0.10714285714285715</v>
       </c>
       <c r="K5" s="0" t="n">
-        <v>0.4910714285714286</v>
+        <v>0.10714285714285715</v>
       </c>
     </row>
     <row r="6">
@@ -541,28 +541,28 @@
         <v>1.0</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>0.6428571428571428</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>0.6428571428571428</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="F6" s="0" t="n">
-        <v>0.55</v>
+        <v>0.09999999999999998</v>
       </c>
       <c r="G6" s="0" t="n">
-        <v>0.55</v>
+        <v>0.09999999999999998</v>
       </c>
       <c r="H6" s="0" t="n">
-        <v>0.55</v>
+        <v>0.09999999999999998</v>
       </c>
       <c r="I6" s="0" t="n">
-        <v>0.55</v>
+        <v>0.09999999999999998</v>
       </c>
       <c r="J6" s="0" t="n">
-        <v>0.55</v>
+        <v>0.09999999999999998</v>
       </c>
       <c r="K6" s="0" t="n">
-        <v>0.55</v>
+        <v>0.09999999999999998</v>
       </c>
     </row>
     <row r="7">
@@ -572,34 +572,34 @@
         </is>
       </c>
       <c r="B7" s="0" t="n">
-        <v>0.6333333333333333</v>
+        <v>0.26666666666666666</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>0.5916666666666667</v>
+        <v>0.1833333333333333</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>0.6333333333333333</v>
+        <v>0.26666666666666666</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>0.6333333333333333</v>
+        <v>0.26666666666666666</v>
       </c>
       <c r="F7" s="0" t="n">
-        <v>0.6333333333333333</v>
+        <v>0.26666666666666666</v>
       </c>
       <c r="G7" s="0" t="n">
-        <v>0.6333333333333333</v>
+        <v>0.26666666666666666</v>
       </c>
       <c r="H7" s="0" t="n">
-        <v>0.6333333333333333</v>
+        <v>0.26666666666666666</v>
       </c>
       <c r="I7" s="0" t="n">
-        <v>0.6333333333333333</v>
+        <v>0.26666666666666666</v>
       </c>
       <c r="J7" s="0" t="n">
-        <v>0.6333333333333333</v>
+        <v>0.26666666666666666</v>
       </c>
       <c r="K7" s="0" t="n">
-        <v>0.6333333333333333</v>
+        <v>0.26666666666666666</v>
       </c>
     </row>
     <row r="8">
@@ -609,34 +609,34 @@
         </is>
       </c>
       <c r="B8" s="0" t="n">
-        <v>0.8819444444444444</v>
+        <v>0.763888888888889</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>0.9166666666666667</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>0.8541666666666667</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>0.8541666666666667</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="F8" s="0" t="n">
-        <v>0.8708333333333333</v>
+        <v>0.7416666666666667</v>
       </c>
       <c r="G8" s="0" t="n">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="H8" s="0" t="n">
-        <v>0.9125000000000001</v>
+        <v>0.8250000000000001</v>
       </c>
       <c r="I8" s="0" t="n">
-        <v>0.836111111111111</v>
+        <v>0.6722222222222222</v>
       </c>
       <c r="J8" s="0" t="n">
-        <v>0.836111111111111</v>
+        <v>0.6722222222222222</v>
       </c>
       <c r="K8" s="0" t="n">
-        <v>0.836111111111111</v>
+        <v>0.6722222222222222</v>
       </c>
     </row>
     <row r="9">
@@ -646,34 +646,34 @@
         </is>
       </c>
       <c r="B9" s="0" t="n">
-        <v>0.8333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>0.8333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>0.8333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>0.780952380952381</v>
+        <v>0.5836734693877551</v>
       </c>
       <c r="F9" s="0" t="n">
-        <v>0.7196969696969697</v>
+        <v>0.4696969696969697</v>
       </c>
       <c r="G9" s="0" t="n">
-        <v>0.7450937950937951</v>
+        <v>0.5174122174122174</v>
       </c>
       <c r="H9" s="0" t="n">
-        <v>0.7183531746031746</v>
+        <v>0.4680059523809524</v>
       </c>
       <c r="I9" s="0" t="n">
-        <v>0.7183531746031746</v>
+        <v>0.4680059523809524</v>
       </c>
       <c r="J9" s="0" t="n">
-        <v>0.7183531746031746</v>
+        <v>0.4680059523809524</v>
       </c>
       <c r="K9" s="0" t="n">
-        <v>0.7008928571428571</v>
+        <v>0.4352678571428571</v>
       </c>
     </row>
     <row r="10">
@@ -683,34 +683,34 @@
         </is>
       </c>
       <c r="B10" s="0" t="n">
-        <v>0.625</v>
+        <v>0.25</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>0.625</v>
+        <v>0.25</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>0.625</v>
+        <v>0.25</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>0.625</v>
+        <v>0.25</v>
       </c>
       <c r="F10" s="0" t="n">
-        <v>0.625</v>
+        <v>0.25</v>
       </c>
       <c r="G10" s="0" t="n">
-        <v>0.625</v>
+        <v>0.25</v>
       </c>
       <c r="H10" s="0" t="n">
-        <v>0.625</v>
+        <v>0.25</v>
       </c>
       <c r="I10" s="0" t="n">
-        <v>0.625</v>
+        <v>0.25</v>
       </c>
       <c r="J10" s="0" t="n">
-        <v>0.625</v>
+        <v>0.25</v>
       </c>
       <c r="K10" s="0" t="n">
-        <v>0.625</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="11">
@@ -720,34 +720,34 @@
         </is>
       </c>
       <c r="B11" s="0" t="n">
-        <v>0.9838709677419355</v>
+        <v>0.967741935483871</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>0.9838709677419355</v>
+        <v>0.967741935483871</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>0.6197916666666666</v>
+        <v>0.3020833333333333</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>0.5514705882352942</v>
+        <v>0.21323529411764705</v>
       </c>
       <c r="F11" s="0" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.08641975308641975</v>
       </c>
       <c r="G11" s="0" t="n">
-        <v>0.5089285714285714</v>
+        <v>0.125</v>
       </c>
       <c r="H11" s="0" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.19753086419753085</v>
       </c>
       <c r="I11" s="0" t="n">
-        <v>0.48355263157894735</v>
+        <v>0.10526315789473684</v>
       </c>
       <c r="J11" s="0" t="n">
-        <v>0.3617346938775511</v>
+        <v>0.03367346938775511</v>
       </c>
       <c r="K11" s="0" t="n">
-        <v>0.4814814814814815</v>
+        <v>0.19753086419753088</v>
       </c>
     </row>
     <row r="12">
@@ -757,34 +757,34 @@
         </is>
       </c>
       <c r="B12" s="0" t="n">
-        <v>0.6266666666666667</v>
+        <v>0.3066666666666667</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>0.6266666666666667</v>
+        <v>0.3066666666666667</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>0.6266666666666667</v>
+        <v>0.3066666666666667</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>0.5988888888888889</v>
+        <v>0.2555555555555556</v>
       </c>
       <c r="F12" s="0" t="n">
-        <v>0.5988888888888889</v>
+        <v>0.2555555555555556</v>
       </c>
       <c r="G12" s="0" t="n">
-        <v>0.5988888888888889</v>
+        <v>0.2555555555555556</v>
       </c>
       <c r="H12" s="0" t="n">
-        <v>0.6527777777777778</v>
+        <v>0.35648148148148145</v>
       </c>
       <c r="I12" s="0" t="n">
-        <v>0.6527777777777778</v>
+        <v>0.35648148148148145</v>
       </c>
       <c r="J12" s="0" t="n">
-        <v>0.6527777777777778</v>
+        <v>0.35648148148148145</v>
       </c>
       <c r="K12" s="0" t="n">
-        <v>0.6527777777777778</v>
+        <v>0.35648148148148145</v>
       </c>
     </row>
     <row r="13">
@@ -794,34 +794,34 @@
         </is>
       </c>
       <c r="B13" s="0" t="n">
-        <v>0.6496212121212122</v>
+        <v>0.29924242424242425</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>0.6496212121212122</v>
+        <v>0.29924242424242425</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>0.6392191142191141</v>
+        <v>0.2784382284382284</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>0.6392191142191141</v>
+        <v>0.2784382284382284</v>
       </c>
       <c r="F13" s="0" t="n">
-        <v>0.6392191142191141</v>
+        <v>0.2784382284382284</v>
       </c>
       <c r="G13" s="0" t="n">
-        <v>0.6392191142191141</v>
+        <v>0.2784382284382284</v>
       </c>
       <c r="H13" s="0" t="n">
-        <v>0.6392191142191141</v>
+        <v>0.2784382284382284</v>
       </c>
       <c r="I13" s="0" t="n">
-        <v>0.6392191142191141</v>
+        <v>0.2784382284382284</v>
       </c>
       <c r="J13" s="0" t="n">
-        <v>0.6392191142191141</v>
+        <v>0.2784382284382284</v>
       </c>
       <c r="K13" s="0" t="n">
-        <v>0.6392191142191141</v>
+        <v>0.2784382284382284</v>
       </c>
     </row>
     <row r="14">
@@ -831,34 +831,34 @@
         </is>
       </c>
       <c r="B14" s="0" t="n">
-        <v>0.6694444444444445</v>
+        <v>0.3564814814814815</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>0.6694444444444445</v>
+        <v>0.3564814814814815</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>0.6694444444444445</v>
+        <v>0.3564814814814815</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>0.6694444444444445</v>
+        <v>0.3564814814814815</v>
       </c>
       <c r="F14" s="0" t="n">
-        <v>0.6694444444444445</v>
+        <v>0.3564814814814815</v>
       </c>
       <c r="G14" s="0" t="n">
-        <v>0.6694444444444445</v>
+        <v>0.3564814814814815</v>
       </c>
       <c r="H14" s="0" t="n">
-        <v>0.6694444444444445</v>
+        <v>0.3564814814814815</v>
       </c>
       <c r="I14" s="0" t="n">
-        <v>0.6694444444444445</v>
+        <v>0.3564814814814815</v>
       </c>
       <c r="J14" s="0" t="n">
-        <v>0.6694444444444445</v>
+        <v>0.3564814814814815</v>
       </c>
       <c r="K14" s="0" t="n">
-        <v>0.6694444444444445</v>
+        <v>0.3564814814814815</v>
       </c>
     </row>
     <row r="15">
@@ -868,34 +868,34 @@
         </is>
       </c>
       <c r="B15" s="0" t="n">
-        <v>0.6833333333333333</v>
+        <v>0.43333333333333335</v>
       </c>
       <c r="C15" s="0" t="n">
-        <v>0.6615384615384616</v>
+        <v>0.36923076923076925</v>
       </c>
       <c r="D15" s="0" t="n">
-        <v>0.5745614035087719</v>
+        <v>0.27192982456140347</v>
       </c>
       <c r="E15" s="0" t="n">
-        <v>0.578048780487805</v>
+        <v>0.30243902439024395</v>
       </c>
       <c r="F15" s="0" t="n">
-        <v>0.5604651162790697</v>
+        <v>0.2883720930232558</v>
       </c>
       <c r="G15" s="0" t="n">
-        <v>0.48703703703703705</v>
+        <v>0.22962962962962963</v>
       </c>
       <c r="H15" s="0" t="n">
-        <v>0.51</v>
+        <v>0.248</v>
       </c>
       <c r="I15" s="0" t="n">
-        <v>0.4766666666666667</v>
+        <v>0.20666666666666667</v>
       </c>
       <c r="J15" s="0" t="n">
-        <v>0.4385964912280702</v>
+        <v>0.18128654970760233</v>
       </c>
       <c r="K15" s="0" t="n">
-        <v>0.40690208667736755</v>
+        <v>0.1508828250401284</v>
       </c>
     </row>
     <row r="16">
@@ -905,34 +905,34 @@
         </is>
       </c>
       <c r="B16" s="0" t="n">
-        <v>0.8230773963332103</v>
+        <v>0.6737787621508552</v>
       </c>
       <c r="C16" s="0" t="n">
-        <v>0.8230773963332103</v>
+        <v>0.6737787621508552</v>
       </c>
       <c r="D16" s="0" t="n">
-        <v>0.6942239858906525</v>
+        <v>0.4440525181265922</v>
       </c>
       <c r="E16" s="0" t="n">
-        <v>0.7357082732082731</v>
+        <v>0.5185696248196248</v>
       </c>
       <c r="F16" s="0" t="n">
-        <v>0.5799482924482925</v>
+        <v>0.2365566628587462</v>
       </c>
       <c r="G16" s="0" t="n">
-        <v>0.6240582585691281</v>
+        <v>0.31802823786519435</v>
       </c>
       <c r="H16" s="0" t="n">
-        <v>0.6291497804795677</v>
+        <v>0.325886524822695</v>
       </c>
       <c r="I16" s="0" t="n">
-        <v>0.6026244588744589</v>
+        <v>0.2771847943722944</v>
       </c>
       <c r="J16" s="0" t="n">
-        <v>0.6026244588744589</v>
+        <v>0.2771847943722944</v>
       </c>
       <c r="K16" s="0" t="n">
-        <v>0.6256786289394984</v>
+        <v>0.3209167241775937</v>
       </c>
     </row>
     <row r="17">
@@ -942,34 +942,34 @@
         </is>
       </c>
       <c r="B17" s="0" t="n">
-        <v>0.6333333333333333</v>
+        <v>0.3466666666666667</v>
       </c>
       <c r="C17" s="0" t="n">
-        <v>0.5928571428571429</v>
+        <v>0.3142857142857143</v>
       </c>
       <c r="D17" s="0" t="n">
-        <v>0.5928571428571429</v>
+        <v>0.3142857142857143</v>
       </c>
       <c r="E17" s="0" t="n">
-        <v>0.5928571428571429</v>
+        <v>0.3142857142857143</v>
       </c>
       <c r="F17" s="0" t="n">
-        <v>0.5928571428571429</v>
+        <v>0.3142857142857143</v>
       </c>
       <c r="G17" s="0" t="n">
-        <v>0.5928571428571429</v>
+        <v>0.3142857142857143</v>
       </c>
       <c r="H17" s="0" t="n">
-        <v>0.5928571428571429</v>
+        <v>0.3142857142857143</v>
       </c>
       <c r="I17" s="0" t="n">
-        <v>0.5928571428571429</v>
+        <v>0.3142857142857143</v>
       </c>
       <c r="J17" s="0" t="n">
-        <v>0.5928571428571429</v>
+        <v>0.3142857142857143</v>
       </c>
       <c r="K17" s="0" t="n">
-        <v>0.5928571428571429</v>
+        <v>0.3142857142857143</v>
       </c>
     </row>
     <row r="18">
@@ -979,34 +979,34 @@
         </is>
       </c>
       <c r="B18" s="0" t="n">
-        <v>0.6973214285714286</v>
+        <v>0.3946428571428572</v>
       </c>
       <c r="C18" s="0" t="n">
-        <v>0.9692234848484849</v>
+        <v>0.9393939393939394</v>
       </c>
       <c r="D18" s="0" t="n">
-        <v>0.9692234848484849</v>
+        <v>0.9393939393939394</v>
       </c>
       <c r="E18" s="0" t="n">
-        <v>0.9692234848484849</v>
+        <v>0.9393939393939394</v>
       </c>
       <c r="F18" s="0" t="n">
-        <v>0.6973214285714286</v>
+        <v>0.3946428571428572</v>
       </c>
       <c r="G18" s="0" t="n">
-        <v>0.984375</v>
+        <v>0.96875</v>
       </c>
       <c r="H18" s="0" t="n">
-        <v>0.984375</v>
+        <v>0.96875</v>
       </c>
       <c r="I18" s="0" t="n">
-        <v>0.9692234848484849</v>
+        <v>0.9393939393939394</v>
       </c>
       <c r="J18" s="0" t="n">
-        <v>0.8422619047619048</v>
+        <v>0.6992857142857143</v>
       </c>
       <c r="K18" s="0" t="n">
-        <v>0.5584893048128342</v>
+        <v>0.26938502673796794</v>
       </c>
     </row>
     <row r="19">
@@ -1016,34 +1016,34 @@
         </is>
       </c>
       <c r="B19" s="0" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="C19" s="0" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="D19" s="0" t="n">
-        <v>0.625</v>
+        <v>0.25</v>
       </c>
       <c r="E19" s="0" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="F19" s="0" t="n">
-        <v>0.625</v>
+        <v>0.25</v>
       </c>
       <c r="G19" s="0" t="n">
-        <v>0.625</v>
+        <v>0.25</v>
       </c>
       <c r="H19" s="0" t="n">
-        <v>0.625</v>
+        <v>0.25</v>
       </c>
       <c r="I19" s="0" t="n">
-        <v>0.625</v>
+        <v>0.25</v>
       </c>
       <c r="J19" s="0" t="n">
-        <v>0.625</v>
+        <v>0.25</v>
       </c>
       <c r="K19" s="0" t="n">
-        <v>0.625</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="20">
@@ -1053,34 +1053,34 @@
         </is>
       </c>
       <c r="B20" s="0" t="n">
-        <v>0.6586309523809524</v>
+        <v>0.31726190476190474</v>
       </c>
       <c r="C20" s="0" t="n">
-        <v>0.6273809523809524</v>
+        <v>0.25476190476190474</v>
       </c>
       <c r="D20" s="0" t="n">
-        <v>0.6273809523809524</v>
+        <v>0.25476190476190474</v>
       </c>
       <c r="E20" s="0" t="n">
-        <v>0.6273809523809524</v>
+        <v>0.25476190476190474</v>
       </c>
       <c r="F20" s="0" t="n">
-        <v>0.6273809523809524</v>
+        <v>0.25476190476190474</v>
       </c>
       <c r="G20" s="0" t="n">
-        <v>0.6273809523809524</v>
+        <v>0.25476190476190474</v>
       </c>
       <c r="H20" s="0" t="n">
-        <v>0.6273809523809524</v>
+        <v>0.25476190476190474</v>
       </c>
       <c r="I20" s="0" t="n">
-        <v>0.6273809523809524</v>
+        <v>0.25476190476190474</v>
       </c>
       <c r="J20" s="0" t="n">
-        <v>0.6273809523809524</v>
+        <v>0.25476190476190474</v>
       </c>
       <c r="K20" s="0" t="n">
-        <v>0.6273809523809524</v>
+        <v>0.25476190476190474</v>
       </c>
     </row>
     <row r="21">
